--- a/outputs/daily/hr_rankings_2026-08-31_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-31_full.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.5</v>
+        <v>67.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>60.3</v>
+        <v>63.3</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -869,12 +869,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Contact streak: 10/25 over last 7 games</t>
+          <t>Contact streak: 11/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -7455,47 +7455,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>700250</t>
+          <t>813841</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Jonah Cox</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-01T01:38:00Z</t>
+          <t>2026-08-31T22:05:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>693821</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7518,65 +7518,61 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>64.90000000000001</v>
+        <v>50.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>16.1</v>
+        <v>40.9</v>
       </c>
       <c r="R26" t="n">
-        <v>67.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U26" t="n">
         <v>53.9</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr"/>
@@ -7593,12 +7589,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -7608,127 +7604,127 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Contact streak: 5/14 over last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.1% barrel, 7.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.7% barrel, 22.6 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>102.5611</t>
+          <t>100.4072</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.5229</t>
+          <t>0.396</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.2534</t>
+          <t>0.189</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3798</t>
+          <t>0.276</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>72.98</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.2643</t>
+          <t>0.241</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>89.93</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.1547</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>26.22</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>92</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7739,47 +7735,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>813841</t>
+          <t>700250</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jonah Cox</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-31T22:05:00Z</t>
+          <t>2026-09-01T01:38:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>693821</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -7788,7 +7784,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7802,30 +7798,30 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>50.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>40.9</v>
+        <v>16.1</v>
       </c>
       <c r="R27" t="n">
-        <v>72.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="S27" t="n">
-        <v>94.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T27" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U27" t="n">
-        <v>46.5</v>
+        <v>53.9</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -7835,7 +7831,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7845,18 +7841,22 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr"/>
@@ -7873,12 +7873,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -7888,127 +7888,127 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/13, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.7% barrel, 22.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.1% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>50.92</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>100.4072</t>
+          <t>102.5611</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>0.5229</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>0.2534</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.3798</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>72.98</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>0.2643</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>89.93</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.1547</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -9188,7 +9188,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>57</v>
+        <v>56.9</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>80</v>
       </c>
       <c r="U32" t="n">
-        <v>40.7</v>
+        <v>39.5</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -18387,56 +18387,56 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>669065</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kyle Stowers</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-31T22:45:00Z</t>
+          <t>2026-08-31T23:40:00Z</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Will Dion</t>
+          <t>Jackson Jobe</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>702021</t>
+          <t>695549</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -18450,26 +18450,26 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>62.3</v>
+        <v>38</v>
       </c>
       <c r="Q65" t="n">
-        <v>25.6</v>
+        <v>43.3</v>
       </c>
       <c r="R65" t="n">
-        <v>50.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="S65" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T65" t="n">
         <v>50</v>
       </c>
       <c r="U65" t="n">
-        <v>24.9</v>
+        <v>10.8</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -18504,7 +18504,7 @@
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr"/>
@@ -18521,12 +18521,12 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -18536,127 +18536,127 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.7% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 3.5 HR allowed</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>54.59</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>91.94</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>103.3199</t>
+          <t>100.8056</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>0.4663</t>
+          <t>0.4224</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>0.2237</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.3432</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>75.28</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>36.19</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>36.41</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>32.06</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>0.2273</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>41.48</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.4394</t>
         </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1764</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>22.68</t>
         </is>
       </c>
       <c r="BG65" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr"/>
@@ -18667,22 +18667,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -18702,12 +18702,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Jackson Jobe</t>
+          <t>Clay Holmes</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>695549</t>
+          <t>605280</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -18716,7 +18716,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -18734,13 +18734,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>38</v>
+        <v>38.3</v>
       </c>
       <c r="Q66" t="n">
-        <v>43.3</v>
+        <v>30.1</v>
       </c>
       <c r="R66" t="n">
-        <v>71.09999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="S66" t="n">
         <v>94.90000000000001</v>
@@ -18749,7 +18749,7 @@
         <v>50</v>
       </c>
       <c r="U66" t="n">
-        <v>10.8</v>
+        <v>57.2</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -18801,27 +18801,27 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Contact streak: 11/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 3.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.8% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
@@ -18831,112 +18831,112 @@
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>100.8056</t>
+          <t>101.5794</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>0.4224</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr">
         <is>
-          <t>0.3432</t>
+          <t>0.3336</t>
         </is>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>36.19</t>
+          <t>36.09</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.1313</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="BD66" t="inlineStr">
         <is>
-          <t>0.4394</t>
+          <t>0.3765</t>
         </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
-          <t>0.1764</t>
+          <t>0.1241</t>
         </is>
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>22.68</t>
+          <t>19.39</t>
         </is>
       </c>
       <c r="BG66" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI66" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ66" t="inlineStr"/>
@@ -18947,56 +18947,56 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-31T23:40:00Z</t>
+          <t>2026-08-31T22:45:00Z</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Clay Holmes</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>605280</t>
+          <t>801139</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -19010,26 +19010,26 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>38.3</v>
+        <v>46.8</v>
       </c>
       <c r="Q67" t="n">
-        <v>30.1</v>
+        <v>28.2</v>
       </c>
       <c r="R67" t="n">
-        <v>74.3</v>
+        <v>48.7</v>
       </c>
       <c r="S67" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T67" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U67" t="n">
-        <v>57.2</v>
+        <v>30.3</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -19081,12 +19081,12 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -19096,12 +19096,12 @@
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Contact streak: 11/29 over last 7 games</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.8% barrel, 7.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 11.3 HR allowed</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
@@ -19111,112 +19111,112 @@
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>45.21</t>
+          <t>44.64</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>101.5794</t>
+          <t>102.6055</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4615</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1943</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr">
         <is>
-          <t>0.3336</t>
+          <t>0.3419</t>
         </is>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>67.13</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>26.68</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>0.1313</t>
+          <t>0.172</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>35.08</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>87.87</t>
         </is>
       </c>
       <c r="BD67" t="inlineStr">
         <is>
-          <t>0.3765</t>
+          <t>0.3497</t>
         </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
-          <t>0.1241</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF67" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>27.6</t>
         </is>
       </c>
       <c r="BG67" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI67" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ67" t="inlineStr"/>
@@ -19227,24 +19227,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>681508</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Julio Rodríguez</t>
+          <t>Mickey Gasper</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>2026-08-31T22:45:00Z</t>
@@ -19257,22 +19257,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Payton Tolle</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>801139</t>
+          <t>669923</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -19290,26 +19290,26 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>46.8</v>
+        <v>28.7</v>
       </c>
       <c r="Q68" t="n">
-        <v>28.2</v>
+        <v>37.9</v>
       </c>
       <c r="R68" t="n">
         <v>48.7</v>
       </c>
       <c r="S68" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T68" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U68" t="n">
-        <v>30.3</v>
+        <v>100</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -19361,27 +19361,27 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 11.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.2% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
@@ -19391,97 +19391,97 @@
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>44.64</t>
+          <t>36.03</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>88.57</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>102.6055</t>
+          <t>98.7087</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>0.4615</t>
+          <t>0.3866</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>0.1943</t>
+          <t>0.1496</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr">
         <is>
-          <t>0.3419</t>
+          <t>0.3228</t>
         </is>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>71.65</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>67.13</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>40.52</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>26.68</t>
+          <t>31.06</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>35.08</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>87.87</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD68" t="inlineStr">
         <is>
-          <t>0.3497</t>
+          <t>0.3969</t>
         </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1416</t>
         </is>
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="BG68" t="inlineStr">
@@ -19507,22 +19507,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>681508</t>
+          <t>669065</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mickey Gasper</t>
+          <t>Kyle Stowers</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -19537,22 +19537,22 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Will Dion</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>702021</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -19570,26 +19570,26 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>28.7</v>
+        <v>62.3</v>
       </c>
       <c r="Q69" t="n">
-        <v>37.9</v>
+        <v>25.6</v>
       </c>
       <c r="R69" t="n">
-        <v>48.7</v>
+        <v>50.2</v>
       </c>
       <c r="S69" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T69" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U69" t="n">
-        <v>100</v>
+        <v>15.3</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -19624,7 +19624,7 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr"/>
@@ -19641,127 +19641,127 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/18, 0 HR</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.2% barrel, 16.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.7% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>36.03</t>
+          <t>54.59</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>88.57</t>
+          <t>91.94</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>98.7087</t>
+          <t>103.3199</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.3866</t>
+          <t>0.4663</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.1496</t>
+          <t>0.2237</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.3228</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>71.65</t>
+          <t>75.28</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>40.52</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>32.06</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>0.1538</t>
+          <t>0.2273</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>0.3969</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>0.1416</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
@@ -19771,12 +19771,12 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -28553,7 +28553,7 @@
         <v>50</v>
       </c>
       <c r="U101" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -28620,7 +28620,7 @@
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL101" t="inlineStr">
@@ -33852,7 +33852,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>80</v>
       </c>
       <c r="U120" t="n">
-        <v>32</v>
+        <v>29.4</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -33952,7 +33952,7 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Contact streak: 6/18 over last 7 games</t>
+          <t>Last 7 games: 6/19, 0 HR</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
@@ -38283,47 +38283,47 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>656775</t>
+          <t>703601</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cedric Mullins</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-31T22:40:00Z</t>
+          <t>2026-08-31T23:40:00Z</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>671737</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -38346,26 +38346,26 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P136" t="n">
-        <v>20.5</v>
+        <v>17.5</v>
       </c>
       <c r="Q136" t="n">
-        <v>48.7</v>
+        <v>47.9</v>
       </c>
       <c r="R136" t="n">
-        <v>41.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="S136" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T136" t="n">
         <v>80</v>
       </c>
       <c r="U136" t="n">
-        <v>30.3</v>
+        <v>31.9</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -38379,7 +38379,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
@@ -38400,7 +38400,7 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr"/>
@@ -38417,12 +38417,12 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
@@ -38432,127 +38432,127 @@
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 1 HR</t>
+          <t>Last 7 games: 4/19, 1 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>97.9263</t>
+          <t>97.7926</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.3157</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>0.094</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.2666</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>70.96</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
+          <t>0.169</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>43.61</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>90.32</t>
+        </is>
+      </c>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>0.3854</t>
+        </is>
+      </c>
+      <c r="BE136" t="inlineStr">
+        <is>
           <t>0.1568</t>
         </is>
       </c>
-      <c r="BA136" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="BB136" t="inlineStr">
-        <is>
-          <t>35.93</t>
-        </is>
-      </c>
-      <c r="BC136" t="inlineStr">
-        <is>
-          <t>89.4</t>
-        </is>
-      </c>
-      <c r="BD136" t="inlineStr">
-        <is>
-          <t>0.4946</t>
-        </is>
-      </c>
-      <c r="BE136" t="inlineStr">
-        <is>
-          <t>0.2019</t>
-        </is>
-      </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH136" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI136" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ136" t="inlineStr"/>
@@ -38563,27 +38563,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>703601</t>
+          <t>607208</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-31T23:40:00Z</t>
+          <t>2026-09-01T01:40:00Z</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -38593,17 +38593,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>671737</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -38626,26 +38626,26 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P137" t="n">
-        <v>17.5</v>
+        <v>26.5</v>
       </c>
       <c r="Q137" t="n">
-        <v>47.9</v>
+        <v>42.1</v>
       </c>
       <c r="R137" t="n">
-        <v>71.09999999999999</v>
+        <v>41.7</v>
       </c>
       <c r="S137" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T137" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U137" t="n">
-        <v>31.9</v>
+        <v>7</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -38680,7 +38680,7 @@
       <c r="AB137" t="inlineStr"/>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr"/>
@@ -38697,27 +38697,27 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 1 HR</t>
+          <t>Last 7 games: 5/30, 0 HR</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
@@ -38727,112 +38727,112 @@
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>97.7926</t>
+          <t>99.2618</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3778</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.3014</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>71.45</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>25.27</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.1425</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>89.05</t>
         </is>
       </c>
       <c r="BD137" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.4177</t>
         </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
-          <t>0.1568</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="BG137" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH137" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI137" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ137" t="inlineStr"/>
@@ -38843,47 +38843,47 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>607208</t>
+          <t>656775</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Cedric Mullins</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-09-01T01:40:00Z</t>
+          <t>2026-08-31T22:40:00Z</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -38892,7 +38892,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -38906,26 +38906,26 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P138" t="n">
-        <v>26.5</v>
+        <v>20.5</v>
       </c>
       <c r="Q138" t="n">
-        <v>42.1</v>
+        <v>48.7</v>
       </c>
       <c r="R138" t="n">
-        <v>41.7</v>
+        <v>41.1</v>
       </c>
       <c r="S138" t="n">
-        <v>100</v>
+        <v>76.2</v>
       </c>
       <c r="T138" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U138" t="n">
-        <v>7</v>
+        <v>28.5</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y138" t="inlineStr">
@@ -38977,127 +38977,127 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/30, 0 HR</t>
+          <t>Last 7 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AL138" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 16.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
-          <t>99.2618</t>
+          <t>97.9263</t>
         </is>
       </c>
       <c r="AR138" t="inlineStr">
         <is>
-          <t>0.3778</t>
+          <t>0.3157</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr">
         <is>
-          <t>0.3014</t>
+          <t>0.2666</t>
         </is>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>71.45</t>
+          <t>70.96</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>45.25</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>0.1425</t>
+          <t>0.1568</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>89.05</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD138" t="inlineStr">
         <is>
-          <t>0.4177</t>
+          <t>0.4946</t>
         </is>
       </c>
       <c r="BE138" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.2019</t>
         </is>
       </c>
       <c r="BF138" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BG138" t="inlineStr">
@@ -39112,7 +39112,7 @@
       </c>
       <c r="BI138" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ138" t="inlineStr"/>
@@ -42057,12 +42057,12 @@
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
@@ -42072,7 +42072,7 @@
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Contact streak: 6/13 over last 7 games</t>
+          <t>Contact streak: 7/14 over last 7 games</t>
         </is>
       </c>
       <c r="AL149" t="inlineStr">
@@ -43177,12 +43177,12 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
@@ -43192,7 +43192,7 @@
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/22, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
@@ -44022,7 +44022,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
@@ -44032,7 +44032,7 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/15, 0 HR</t>
+          <t>Last 7 games: 1/16, 0 HR</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
@@ -46736,7 +46736,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="M166" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>78</v>
       </c>
       <c r="U166" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="V166" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ166" t="inlineStr">
@@ -46836,7 +46836,7 @@
       </c>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/12, 0 HR</t>
+          <t>Last 7 games: 2/13, 0 HR</t>
         </is>
       </c>
       <c r="AL166" t="inlineStr">
@@ -46967,27 +46967,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>823550</t>
+          <t>678391</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Sung-Mun Song</t>
+          <t>Jorbit Vivas</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-08-31T22:40:00Z</t>
+          <t>2026-08-31T22:45:00Z</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -46997,17 +46997,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -47016,7 +47016,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -47034,22 +47034,22 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>11.9</v>
+        <v>5.1</v>
       </c>
       <c r="Q167" t="n">
-        <v>52</v>
+        <v>46.6</v>
       </c>
       <c r="R167" t="n">
-        <v>68.8</v>
+        <v>50.2</v>
       </c>
       <c r="S167" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T167" t="n">
         <v>80</v>
       </c>
       <c r="U167" t="n">
-        <v>0</v>
+        <v>40.3</v>
       </c>
       <c r="V167" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
@@ -47084,7 +47084,7 @@
       <c r="AB167" t="inlineStr"/>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD167" t="inlineStr"/>
@@ -47101,27 +47101,27 @@
       </c>
       <c r="AH167" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/6, 0 HR</t>
+          <t>Contact streak: 7/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 23.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
@@ -47131,97 +47131,97 @@
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>83.66</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
         <is>
-          <t>96.9545</t>
+          <t>95.131</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.324</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.0799</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.3024</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>41.53</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.0862</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>90.65</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD167" t="inlineStr">
         <is>
-          <t>0.4349</t>
+          <t>0.4285</t>
         </is>
       </c>
       <c r="BE167" t="inlineStr">
         <is>
-          <t>0.1723</t>
+          <t>0.1655</t>
         </is>
       </c>
       <c r="BF167" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BG167" t="inlineStr">
@@ -47231,12 +47231,12 @@
       </c>
       <c r="BH167" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI167" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ167" t="inlineStr"/>
@@ -47247,27 +47247,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>668800</t>
+          <t>823550</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Andrew Knizner</t>
+          <t>Sung-Mun Song</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-31T22:05:00Z</t>
+          <t>2026-08-31T22:40:00Z</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -47277,17 +47277,17 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Bryce Elder</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>693821</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -47296,7 +47296,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
@@ -47310,26 +47310,26 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P168" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="Q168" t="n">
-        <v>40.9</v>
+        <v>52</v>
       </c>
       <c r="R168" t="n">
-        <v>72.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="S168" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T168" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U168" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="V168" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y168" t="inlineStr">
@@ -47364,7 +47364,7 @@
       <c r="AB168" t="inlineStr"/>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD168" t="inlineStr"/>
@@ -47381,27 +47381,27 @@
       </c>
       <c r="AH168" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 1 HR</t>
+          <t>Last 7 games: 0/6, 0 HR</t>
         </is>
       </c>
       <c r="AL168" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.7% barrel, 22.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 23.9 HR allowed</t>
         </is>
       </c>
       <c r="AM168" t="inlineStr">
@@ -47411,57 +47411,57 @@
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AQ168" t="inlineStr">
         <is>
-          <t>96.4187</t>
+          <t>96.9545</t>
         </is>
       </c>
       <c r="AR168" t="inlineStr">
         <is>
-          <t>0.3125</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>0.088</t>
         </is>
       </c>
       <c r="AT168" t="inlineStr">
         <is>
-          <t>0.2773</t>
+          <t>0.257</t>
         </is>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>32.72</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -47471,52 +47471,52 @@
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>0.1452</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>89.93</t>
+          <t>90.65</t>
         </is>
       </c>
       <c r="BD168" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.4349</t>
         </is>
       </c>
       <c r="BE168" t="inlineStr">
         <is>
-          <t>0.1547</t>
+          <t>0.1723</t>
         </is>
       </c>
       <c r="BF168" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="BG168" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH168" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI168" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ168" t="inlineStr"/>
@@ -47527,27 +47527,27 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>678391</t>
+          <t>668800</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Jorbit Vivas</t>
+          <t>Andrew Knizner</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-31T22:45:00Z</t>
+          <t>2026-08-31T22:05:00Z</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -47557,17 +47557,17 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>Bryce Elder</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>693821</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -47590,26 +47590,26 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P169" t="n">
-        <v>5.1</v>
+        <v>11.2</v>
       </c>
       <c r="Q169" t="n">
-        <v>46.6</v>
+        <v>40.9</v>
       </c>
       <c r="R169" t="n">
-        <v>50.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="S169" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="T169" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U169" t="n">
-        <v>36.5</v>
+        <v>42</v>
       </c>
       <c r="V169" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y169" t="inlineStr">
@@ -47661,27 +47661,27 @@
       </c>
       <c r="AH169" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 5/18, 1 HR</t>
         </is>
       </c>
       <c r="AL169" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 10.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.7% barrel, 22.6 HR allowed</t>
         </is>
       </c>
       <c r="AM169" t="inlineStr">
@@ -47691,112 +47691,112 @@
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>25.37</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>83.66</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ169" t="inlineStr">
         <is>
-          <t>95.131</t>
+          <t>96.4187</t>
         </is>
       </c>
       <c r="AR169" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>0.3125</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>0.0799</t>
+          <t>0.105</t>
         </is>
       </c>
       <c r="AT169" t="inlineStr">
         <is>
-          <t>0.3024</t>
+          <t>0.2773</t>
         </is>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>41.53</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>32.72</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>0.0862</t>
+          <t>0.1452</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>89.93</t>
         </is>
       </c>
       <c r="BD169" t="inlineStr">
         <is>
-          <t>0.4285</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="BE169" t="inlineStr">
         <is>
-          <t>0.1655</t>
+          <t>0.1547</t>
         </is>
       </c>
       <c r="BF169" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>26.22</t>
         </is>
       </c>
       <c r="BG169" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH169" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="BI169" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ169" t="inlineStr"/>
@@ -48696,7 +48696,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -48729,7 +48729,7 @@
         <v>50</v>
       </c>
       <c r="U173" t="n">
-        <v>42.3</v>
+        <v>43.2</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
@@ -48781,12 +48781,12 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
@@ -48796,7 +48796,7 @@
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 1 HR</t>
+          <t>Last 7 games: 6/21, 1 HR</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
@@ -49256,7 +49256,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>80</v>
       </c>
       <c r="U175" t="n">
-        <v>38.3</v>
+        <v>29.7</v>
       </c>
       <c r="V175" t="inlineStr">
         <is>
@@ -49341,12 +49341,12 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
@@ -49356,7 +49356,7 @@
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Contact streak: 9/24 over last 7 games</t>
+          <t>Last 7 games: 7/22, 0 HR</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
@@ -59106,7 +59106,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.5</v>
+        <v>67.7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -59139,7 +59139,7 @@
         <v>80</v>
       </c>
       <c r="U2" t="n">
-        <v>60.3</v>
+        <v>63.3</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -59191,12 +59191,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -59206,7 +59206,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Contact streak: 10/25 over last 7 games</t>
+          <t>Contact streak: 11/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
